--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_945_Mexico_Pacific.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_945_Mexico_Pacific.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf4447e96b8434baf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4357d51cc9734965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7c1193ad33f84a49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R224a2d4234fd45c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb37db3397dfd4608"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3a05cbee452e4f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3a0f828e5ba44742"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rdcd2822824574e3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R388978a42ae5400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5b0e93a7180545c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R545823dc660642cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3ca634fd3d684bd0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ945CommercialTable" displayName="EEZ945CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ945CommercialTable" displayName="EEZ945CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ945FunctionalTable" displayName="EEZ945FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ945FunctionalTable" displayName="EEZ945FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ945ValidationTable" displayName="EEZ945ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ945ValidationTable" displayName="EEZ945ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -9806,7 +9760,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb071aa6fea7a4148"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84e67e513fc54b45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9816,20 +9770,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9837,660 +9781,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>273372.4825</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.563934106919485</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>36.638198133508716</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>273372.4825</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>41.50059006070159</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$137,A2,'Species'!$U$2:$U$137))</x:f>
-        <x:v>11345119.33010882</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.563934106919485</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>36.638198133508716</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>10015875.178084144</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1329244.1520246752</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1327137297930001</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.13271372979300003</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>12169.482604138999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.338311195717279</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2179.270779557378</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>12169.482604138999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2200.841692173222</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$137,A3,'Species'!$U$2:$U$137))</x:f>
-        <x:v>26783104.68736586</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.338311195717279</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2179.270779557378</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>26520597.841531944</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>262506.8458339162</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.009898225047658</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.009898225047658001</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>156251.4075409981</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1207438077424494</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>132.05164258334227</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>156251.4075409981</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>239.75906460965012</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$137,A4,'Species'!$U$2:$U$137))</x:f>
-        <x:v>37462691.315970935</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1207438077424494</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>132.05164258334227</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20633255.021748032</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>16829436.294222903</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.8156462117336407</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.8156462117336408</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>37928.2351066383</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.7698201660295982</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>588.5998756727857</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>37928.2351066383</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>761.140896333276</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$137,A5,'Species'!$U$2:$U$137))</x:f>
-        <x:v>28868730.865405902</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.7698201660295982</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>588.5998756727857</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>22324554.46825549</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6544176.397150412</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2931380514874748</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.29313805148747474</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>395472.3371909046</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.8723669091804065</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>74.53614188284091</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>395472.3371909046</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>74.64945800342021</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$137,A6,'Species'!$U$2:$U$137))</x:f>
-        <x:v>29521795.62664687</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.8723669091804065</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>74.53614188284091</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>29476982.235599965</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>44813.39104690403</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.001520284223423</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0015202842234230463</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>44429.685367889695</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.322440243159607</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>21.010686521744592</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>44429.685367889695</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>36.62777447104267</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$137,A7,'Species'!$U$2:$U$137))</x:f>
-        <x:v>1627360.4954744482</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.322440243159607</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>21.010686521744592</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>933498.1915244729</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>693862.3039499753</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7432926065093344</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7432926065093344</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>770078.4488474998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4447260526391412</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>278.4364273483092</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>770078.4488474998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>362.61541243006275</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$137,A8,'Species'!$U$2:$U$137))</x:f>
-        <x:v>279242314.3323391</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4447260526391412</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>278.4364273483092</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>214417892.07502553</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>64824422.25731358</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.3023274859666623</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.30232748596666226</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>334718.76992059965</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6986200266081095</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>499.59723555678227</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>334718.76992059965</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>810.0498906945625</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$137,A9,'Species'!$U$2:$U$137))</x:f>
-        <x:v>271138902.98760015</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6986200266081095</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>499.59723555678227</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>167224572.14129823</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>103914330.84630191</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.621405870654573</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.6214058706545732</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>30342.6622833721</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.594874476458923</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>393.4363446513808</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>30342.6622833721</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>397.7637610843958</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$137,A10,'Species'!$U$2:$U$137))</x:f>
-        <x:v>12069211.47114773</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.594874476458923</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>393.4363446513808</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>11937906.135761239</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>131305.33538649045</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.01099902561582</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.010999025615819818</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>51169.99068966109</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.038833102598189</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1093.5360445657748</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>51169.99068966109</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1303.8985957140235</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$137,A11,'Species'!$U$2:$U$137))</x:f>
-        <x:v>66720479.00294875</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.038833102598189</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1093.5360445657748</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>55956229.21923951</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>10764249.783709243</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1923691058869306</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.19236910588693057</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>56538.515952865506</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.365199561180799</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2318.459752797205</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>56538.515952865506</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2460.681178091843</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$137,A12,'Species'!$U$2:$U$137))</x:f>
-        <x:v>139123262.04246154</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.365199561180799</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2318.459752797205</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>131082273.7196014</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>8040988.3228601515</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.061343064128264</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.06134306412826391</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R644a0a5e651d4ed7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ef73d3b144f42b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10500,20 +10015,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10521,1146 +10026,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>15884</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9952228657768822</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>989.0605180791426</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>15884</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1041.218851288379</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$137,A2,'Species'!$U$2:$U$137))</x:f>
-        <x:v>16538720.233864613</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9952228657768822</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>989.0605180791426</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>15710237.269169101</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>828482.9646955114</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0527352292967203</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.052735229296720164</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>144859.8609894506</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.430276088424329</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>269.32464025892784</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>144859.8609894506</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>271.15659671144243</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$137,A3,'Species'!$U$2:$U$137))</x:f>
-        <x:v>39279706.90599207</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.430276088424329</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>269.32464025892784</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>39014329.94894207</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>265376.95704999566</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0068020380562037</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.006802038056203801</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>201.4679504609</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>201.4679504609</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$137,A4,'Species'!$U$2:$U$137))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>451030.5594408555</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>451030.5594408555</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>18905.7583357119</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.0852421851728864</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>12.168643983014084</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>18905.7583357119</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>26.473267004560636</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$137,A5,'Species'!$U$2:$U$137))</x:f>
-        <x:v>500497.18834499904</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.0852421851728864</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>12.168643983014084</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>230057.44241617896</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>270439.7459288201</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.1755313937620353</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.1755313937620355</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1268.7575989292</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.424999999999999</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2660.725059798803</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1268.7575989292</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2700.4993993683584</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$137,A6,'Species'!$U$2:$U$137))</x:f>
-        <x:v>3426279.133852345</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.424999999999999</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2660.725059798803</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3375815.1382810813</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>50463.9955712636</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0149486845411089</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.01494868454110884</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>82978.68761039329</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.388444374874288</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2445.9319771427245</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>82978.68761039329</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2476.060571972316</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$137,A7,'Species'!$U$2:$U$137))</x:f>
-        <x:v>205460256.70610255</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.388444374874288</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2445.9319771427245</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>202960225.44759774</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2500031.258504808</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0123178383990823</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01231783839908224</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>10996.4621928257</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6037909268773896</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>401.597431825812</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>10996.4621928257</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>428.90066732513117</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$137,A8,'Species'!$U$2:$U$137))</x:f>
-        <x:v>4716389.972718518</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6037909268773896</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>401.597431825812</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4416150.975808438</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>300238.9969100803</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.067986578935997</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.06798657893599695</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>10696.894637037803</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.555347493741763</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>359.2092351799692</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>10696.894637037803</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>392.93280633001046</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$137,A9,'Species'!$U$2:$U$137))</x:f>
-        <x:v>4203160.828747703</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.555347493741763</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>359.2092351799692</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3842423.3413710636</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>360737.48737663915</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0938828065852628</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.09388280658526289</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>40173.52849683539</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.15791462260894</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1438.5157545032594</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>40173.52849683539</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1543.4066000728446</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$137,A10,'Species'!$U$2:$U$137))</x:f>
-        <x:v>62004089.03023024</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.15791462260894</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1438.5157545032594</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>57790253.65668335</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4213835.373546891</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0729160214208469</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.07291602142084676</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>59245.6288788689</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.50738929566514</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>321.65425117140785</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>59245.6288788689</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>440.0134912175357</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$137,A11,'Species'!$U$2:$U$137))</x:f>
-        <x:v>26068876.00236956</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.50738929566514</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>321.65425117140785</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>19056608.39221171</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>7012267.610157851</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.367970389370215</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.3679703893702151</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>14108.2772191283</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.984933378219125</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>965.9026959103153</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>14108.2772191283</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1867.9796884797804</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$137,A12,'Species'!$U$2:$U$137))</x:f>
-        <x:v>26353975.284773666</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.984933378219125</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>965.9026959103153</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>13627223.00060611</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>12726752.284167556</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.9339211872882316</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.9339211872882316</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>621583.0467917802</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.4745978412325913</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>298.26194198994017</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>621583.0467917802</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>394.0397170429011</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$137,A13,'Species'!$U$2:$U$137))</x:f>
-        <x:v>244928407.8764974</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.4745978412325913</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>298.26194198994017</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>185394566.6441402</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>59533841.232357174</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3211196655327593</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.3211196655327594</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>223157.09814161708</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.1363818250432933</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>136.89318405471815</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>223157.09814161708</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>275.9648257054561</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$137,A14,'Species'!$U$2:$U$137))</x:f>
-        <x:v>61583509.69358673</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.1363818250432933</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>136.89318405471815</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>30548685.709017187</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>31034823.984569542</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.015913557793711</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.0159135577937108</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>48367.27341117641</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.889712146611729</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>775.7327851376037</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>48367.27341117641</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>948.5480803235325</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$137,A15,'Species'!$U$2:$U$137))</x:f>
-        <x:v>45878684.34465482</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.889712146611729</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>775.7327851376037</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>37520079.712763846</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>8358604.631890975</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2227768356538828</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.22277683565388284</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>44614.29266608449</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.3223515671350405</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>21.006396911739092</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>44614.29266608449</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>36.55899896898773</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$137,A16,'Species'!$U$2:$U$137))</x:f>
-        <x:v>1631053.8795814996</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.3223515671350405</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>21.006396911739092</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>937185.5396802613</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>693868.3399012383</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.7403745688798877</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.7403745688798877</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>97005.7786621292</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.884602668512567</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>76.66597593981577</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>97005.7786621292</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>117.45501629635883</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$137,A17,'Species'!$U$2:$U$137))</x:f>
-        <x:v>11393815.313601363</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.884602668512567</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>76.66597593981577</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>7437042.692933891</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>3956772.6206674725</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.532035754538144</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.5320357545381439</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4360.0205852899</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.553366793955011</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>357.5747090648849</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4360.0205852899</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>452.85848570547296</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$137,A18,'Species'!$U$2:$U$137))</x:f>
-        <x:v>1974472.319899074</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.553366793955011</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>357.5747090648849</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1559033.0923019452</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>415439.22759712883</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.266472360111179</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.266472360111179</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>47396.5653073851</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.838265894671331</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>689.0740494377617</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>47396.5653073851</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>742.820431959114</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$137,A19,'Species'!$U$2:$U$137))</x:f>
-        <x:v>35207137.11501016</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.838265894671331</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>689.0740494377617</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>32659743.185801182</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>2547393.9292089753</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0779979779607225</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.07799797796072243</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>638740.3834228248</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.858626762434253</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>72.21489139361545</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>638740.3834228248</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>130.62299029176233</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$137,A20,'Species'!$U$2:$U$137))</x:f>
-        <x:v>83434178.9027962</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.858626762434253</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>72.21489139361545</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>46126567.41759558</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>37307611.485200614</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.8088096204394593</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.8088096204394594</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>37928.2351066383</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.7698201660295982</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>588.5998756727857</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>37928.2351066383</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>761.140896333276</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$137,A21,'Species'!$U$2:$U$137))</x:f>
-        <x:v>28868730.865405902</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.7698201660295982</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>588.5998756727857</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>22324554.46825549</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>6544176.397150412</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.2931380514874748</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.29313805148747474</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R985a15fc5c994d10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39d1854e16b84de3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11835,7 +10596,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -11934,7 +10695,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>903902972.1574703</x:v>
+        <x:v>690523636.22767</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11948,7 +10709,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>903902972.1574702</x:v>
+        <x:v>724981813.6350174</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11962,7 +10723,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-213379335.92980027</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11976,7 +10737,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-178921158.52245283</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11987,9 +10748,9 @@
         <x:v>EEZ_945</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12001,47 +10762,19 @@
         <x:v>EEZ_945</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_945</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_945</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04d182fabcef4df4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20f2a2350ad94b70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12088,7 +10821,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
